--- a/event_feedback_forms/015_skydiving_event_feedback_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/015_skydiving_event_feedback_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E35"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,76 +577,76 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>rating</t>
+          <t>event_date_time</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rating</t>
+          <t>Event Date and Time</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>event_date</t>
+          <t>event_location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Event Date</t>
+          <t>Event Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>event_time</t>
+          <t>feedback</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Event Time</t>
+          <t>Feedback</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -658,64 +658,64 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>event_location</t>
+          <t>overall_rating</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Event Location</t>
+          <t>Overall Rating</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>event_notes</t>
+          <t>enjoyed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Event Notes</t>
+          <t>Enjoyed The Event</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>feedback</t>
+          <t>would_recommend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Feedback</t>
+          <t>Would Recommend</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -727,18 +727,18 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rating2</t>
+          <t>suggestions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Overall Rating</t>
+          <t>Suggestions</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -750,499 +750,16 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>suggestions</t>
+          <t>additional_comments</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suggestions</t>
+          <t>Additional Comments</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>additional_comments</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Additional Comments</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>rating3</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Enjoyed The Event</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>would_recommend</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Would Recommend</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>rating4</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Overall Rating 2</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>rating5</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Rating 2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>rating6</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Overall Rating 3</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>rating7</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Overall Rating 4</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>rating8</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Overall Rating 5</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>rating9</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Overall Rating 6</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>rating10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Overall Rating 7</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>rating11</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Overall Rating 8</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>rating12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Overall Rating 9</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>rating13</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Overall Rating 10</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>overall_suggestions</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Overall Suggestions</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>overall_comments</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Overall Comments</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>overall_rating_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Overall Rating 2</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>overall_rating_3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Overall Rating 3</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>overall_rating_4</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Overall Rating 4</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>overall_rating_5</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Overall Rating 5</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>overall_rating_6</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Overall Rating 6</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>overall_rating_7</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Overall Rating 7</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1287,7 +804,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>rating3_choices</t>
+          <t>enjoyed_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1304,7 +821,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>rating3_choices</t>
+          <t>enjoyed_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
